--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:27:54+00:00</t>
+    <t>2023-04-26T14:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:43:04+00:00</t>
+    <t>2023-04-27T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T16:49:23+00:00</t>
+    <t>2023-05-02T12:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T12:59:07+00:00</t>
+    <t>2023-05-02T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T13:06:55+00:00</t>
+    <t>2023-05-02T14:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:33:57+00:00</t>
+    <t>2023-07-18T09:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:12+00:00</t>
+    <t>2023-07-18T09:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:49+00:00</t>
+    <t>2023-07-18T09:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4374" uniqueCount="642">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:37:51+00:00</t>
+    <t>2023-09-19T16:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -143,6 +143,10 @@
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
+  </si>
+  <si>
     <t>Event</t>
   </si>
   <si>
@@ -522,7 +526,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -609,7 +613,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -1078,7 +1082,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1136,7 +1140,7 @@
     <t>Often just a dateTime for Vital Signs.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -1171,7 +1175,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1221,7 +1225,7 @@
     <t>Vital Signs value are recorded using the Quantity data type. For supporting observations such as Cuff size could use other datatypes such as CodeableConcept.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>9. SHALL contain exactly one [1..1] value with @xsi:type="PQ" (CONF:7305).</t>
@@ -1496,9 +1500,6 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
@@ -1549,7 +1550,7 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1890,7 +1891,7 @@
     <t>Used when reporting vital signs panel components.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1912,7 +1913,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1924,7 +1925,7 @@
     <t>Used when reporting systolic and diastolic blood pressure.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -1977,7 +1978,7 @@
     <t>Vital Sign Value recorded with UCUM.</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Common UCUM units for recording Vital Signs.</t>
@@ -2011,6 +2012,9 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2468,19 +2472,19 @@
         <v>36</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AM1" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN1" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AO1" t="s" s="2">
         <v>36</v>
@@ -2491,10 +2495,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2505,7 +2509,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>36</v>
@@ -2514,19 +2518,19 @@
         <v>36</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2576,13 +2580,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>36</v>
@@ -2611,10 +2615,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2625,7 +2629,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>36</v>
@@ -2634,16 +2638,16 @@
         <v>36</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2694,19 +2698,19 @@
         <v>36</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>36</v>
@@ -2718,7 +2722,7 @@
         <v>36</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO3" t="s" s="2">
         <v>36</v>
@@ -2729,10 +2733,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2743,7 +2747,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>36</v>
@@ -2755,13 +2759,13 @@
         <v>36</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2812,13 +2816,13 @@
         <v>36</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>36</v>
@@ -2836,7 +2840,7 @@
         <v>36</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>36</v>
@@ -2847,14 +2851,14 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -2873,16 +2877,16 @@
         <v>36</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2920,19 +2924,19 @@
         <v>36</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>34</v>
@@ -2941,10 +2945,10 @@
         <v>35</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>36</v>
@@ -2956,7 +2960,7 @@
         <v>36</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>36</v>
@@ -2967,10 +2971,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2981,7 +2985,7 @@
         <v>34</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>36</v>
@@ -2990,19 +2994,19 @@
         <v>36</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3052,19 +3056,19 @@
         <v>36</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>36</v>
@@ -3076,7 +3080,7 @@
         <v>36</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>36</v>
@@ -3087,10 +3091,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3101,7 +3105,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>36</v>
@@ -3110,19 +3114,19 @@
         <v>36</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3172,19 +3176,19 @@
         <v>36</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>36</v>
@@ -3196,7 +3200,7 @@
         <v>36</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>36</v>
@@ -3207,10 +3211,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3221,7 +3225,7 @@
         <v>34</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>36</v>
@@ -3230,19 +3234,19 @@
         <v>36</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3292,19 +3296,19 @@
         <v>36</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>36</v>
@@ -3316,7 +3320,7 @@
         <v>36</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>36</v>
@@ -3327,10 +3331,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3350,19 +3354,19 @@
         <v>36</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3412,7 +3416,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>34</v>
@@ -3421,10 +3425,10 @@
         <v>35</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>36</v>
@@ -3436,7 +3440,7 @@
         <v>36</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>36</v>
@@ -3447,10 +3451,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3470,19 +3474,19 @@
         <v>36</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3508,13 +3512,13 @@
         <v>36</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>36</v>
@@ -3532,7 +3536,7 @@
         <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>34</v>
@@ -3541,10 +3545,10 @@
         <v>35</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>36</v>
@@ -3553,10 +3557,10 @@
         <v>36</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>36</v>
@@ -3567,10 +3571,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3590,19 +3594,19 @@
         <v>36</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3628,13 +3632,13 @@
         <v>36</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>36</v>
@@ -3652,7 +3656,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>34</v>
@@ -3661,10 +3665,10 @@
         <v>35</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>36</v>
@@ -3673,10 +3677,10 @@
         <v>36</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>36</v>
@@ -3687,10 +3691,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3701,28 +3705,28 @@
         <v>34</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3772,19 +3776,19 @@
         <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>36</v>
@@ -3796,7 +3800,7 @@
         <v>36</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>36</v>
@@ -3807,10 +3811,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3821,7 +3825,7 @@
         <v>34</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>36</v>
@@ -3833,16 +3837,16 @@
         <v>36</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3868,13 +3872,13 @@
         <v>36</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>36</v>
@@ -3892,19 +3896,19 @@
         <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>36</v>
@@ -3916,7 +3920,7 @@
         <v>36</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>36</v>
@@ -3927,21 +3931,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>36</v>
@@ -3953,16 +3957,16 @@
         <v>36</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4012,19 +4016,19 @@
         <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>36</v>
@@ -4036,7 +4040,7 @@
         <v>36</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>36</v>
@@ -4047,14 +4051,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4073,16 +4077,16 @@
         <v>36</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4132,7 +4136,7 @@
         <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>34</v>
@@ -4156,7 +4160,7 @@
         <v>36</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>36</v>
@@ -4167,14 +4171,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4193,16 +4197,16 @@
         <v>36</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4240,19 +4244,19 @@
         <v>36</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>34</v>
@@ -4261,10 +4265,10 @@
         <v>35</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>36</v>
@@ -4276,7 +4280,7 @@
         <v>36</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>36</v>
@@ -4287,23 +4291,23 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>36</v>
@@ -4315,16 +4319,16 @@
         <v>36</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4374,7 +4378,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>34</v>
@@ -4383,10 +4387,10 @@
         <v>35</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>36</v>
@@ -4398,7 +4402,7 @@
         <v>36</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>36</v>
@@ -4409,14 +4413,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4429,25 +4433,25 @@
         <v>36</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>36</v>
@@ -4484,19 +4488,19 @@
         <v>36</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>34</v>
@@ -4505,10 +4509,10 @@
         <v>35</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>36</v>
@@ -4520,7 +4524,7 @@
         <v>36</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>36</v>
@@ -4531,10 +4535,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4554,20 +4558,20 @@
         <v>36</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>36</v>
@@ -4616,7 +4620,7 @@
         <v>36</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>34</v>
@@ -4625,25 +4629,25 @@
         <v>35</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>36</v>
@@ -4651,14 +4655,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4674,22 +4678,22 @@
         <v>36</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>36</v>
@@ -4738,7 +4742,7 @@
         <v>36</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>34</v>
@@ -4747,22 +4751,22 @@
         <v>35</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>36</v>
@@ -4773,14 +4777,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4796,19 +4800,19 @@
         <v>36</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4858,7 +4862,7 @@
         <v>36</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>34</v>
@@ -4867,22 +4871,22 @@
         <v>35</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>36</v>
@@ -4893,10 +4897,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4904,34 +4908,34 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>36</v>
@@ -4956,13 +4960,13 @@
         <v>36</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>36</v>
@@ -4980,34 +4984,34 @@
         <v>36</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>36</v>
@@ -5015,10 +5019,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5026,13 +5030,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>36</v>
@@ -5041,19 +5045,19 @@
         <v>36</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>36</v>
@@ -5078,29 +5082,29 @@
         <v>36</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>34</v>
@@ -5109,10 +5113,10 @@
         <v>35</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>36</v>
@@ -5121,13 +5125,13 @@
         <v>36</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>36</v>
@@ -5135,26 +5139,26 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>36</v>
@@ -5163,19 +5167,19 @@
         <v>36</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>36</v>
@@ -5200,13 +5204,13 @@
         <v>36</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>36</v>
@@ -5224,7 +5228,7 @@
         <v>36</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>34</v>
@@ -5233,10 +5237,10 @@
         <v>35</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>36</v>
@@ -5245,13 +5249,13 @@
         <v>36</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>36</v>
@@ -5259,10 +5263,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5273,7 +5277,7 @@
         <v>34</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>36</v>
@@ -5285,13 +5289,13 @@
         <v>36</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5342,13 +5346,13 @@
         <v>36</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>36</v>
@@ -5366,7 +5370,7 @@
         <v>36</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>36</v>
@@ -5377,14 +5381,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5403,16 +5407,16 @@
         <v>36</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5450,19 +5454,19 @@
         <v>36</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>34</v>
@@ -5471,10 +5475,10 @@
         <v>35</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>36</v>
@@ -5486,7 +5490,7 @@
         <v>36</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>36</v>
@@ -5497,10 +5501,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5508,34 +5512,34 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>36</v>
@@ -5584,7 +5588,7 @@
         <v>36</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>34</v>
@@ -5593,10 +5597,10 @@
         <v>35</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>36</v>
@@ -5605,10 +5609,10 @@
         <v>36</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>36</v>
@@ -5619,10 +5623,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5633,7 +5637,7 @@
         <v>34</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>36</v>
@@ -5645,13 +5649,13 @@
         <v>36</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5702,13 +5706,13 @@
         <v>36</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>36</v>
@@ -5726,7 +5730,7 @@
         <v>36</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>36</v>
@@ -5737,14 +5741,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5763,16 +5767,16 @@
         <v>36</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5810,19 +5814,19 @@
         <v>36</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>34</v>
@@ -5831,10 +5835,10 @@
         <v>35</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>36</v>
@@ -5846,7 +5850,7 @@
         <v>36</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>36</v>
@@ -5857,10 +5861,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5868,41 +5872,41 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>36</v>
@@ -5944,19 +5948,19 @@
         <v>36</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>36</v>
@@ -5965,10 +5969,10 @@
         <v>36</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>36</v>
@@ -5979,10 +5983,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5993,7 +5997,7 @@
         <v>34</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>36</v>
@@ -6002,19 +6006,19 @@
         <v>36</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6064,19 +6068,19 @@
         <v>36</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>36</v>
@@ -6085,10 +6089,10 @@
         <v>36</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>36</v>
@@ -6099,10 +6103,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6110,41 +6114,41 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>36</v>
@@ -6186,19 +6190,19 @@
         <v>36</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>36</v>
@@ -6207,10 +6211,10 @@
         <v>36</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>36</v>
@@ -6221,10 +6225,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6235,7 +6239,7 @@
         <v>34</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>36</v>
@@ -6244,22 +6248,22 @@
         <v>36</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>36</v>
@@ -6308,19 +6312,19 @@
         <v>36</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>36</v>
@@ -6329,10 +6333,10 @@
         <v>36</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>36</v>
@@ -6343,10 +6347,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6357,7 +6361,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>36</v>
@@ -6366,22 +6370,22 @@
         <v>36</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>36</v>
@@ -6430,19 +6434,19 @@
         <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>36</v>
@@ -6451,10 +6455,10 @@
         <v>36</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>36</v>
@@ -6465,10 +6469,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6479,7 +6483,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>36</v>
@@ -6488,22 +6492,22 @@
         <v>36</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>36</v>
@@ -6552,19 +6556,19 @@
         <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>36</v>
@@ -6573,10 +6577,10 @@
         <v>36</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>36</v>
@@ -6587,45 +6591,45 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>36</v>
@@ -6650,13 +6654,13 @@
         <v>36</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>36</v>
@@ -6674,45 +6678,45 @@
         <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6723,7 +6727,7 @@
         <v>34</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>36</v>
@@ -6735,13 +6739,13 @@
         <v>36</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6792,13 +6796,13 @@
         <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>36</v>
@@ -6816,7 +6820,7 @@
         <v>36</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>36</v>
@@ -6827,14 +6831,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6853,16 +6857,16 @@
         <v>36</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6900,19 +6904,19 @@
         <v>36</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>34</v>
@@ -6921,10 +6925,10 @@
         <v>35</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>36</v>
@@ -6936,7 +6940,7 @@
         <v>36</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>36</v>
@@ -6947,10 +6951,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6970,22 +6974,22 @@
         <v>36</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>36</v>
@@ -7022,17 +7026,17 @@
         <v>36</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>34</v>
@@ -7041,10 +7045,10 @@
         <v>35</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>36</v>
@@ -7053,10 +7057,10 @@
         <v>36</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>36</v>
@@ -7067,23 +7071,23 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>36</v>
@@ -7092,22 +7096,22 @@
         <v>36</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>36</v>
@@ -7156,7 +7160,7 @@
         <v>36</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>34</v>
@@ -7165,10 +7169,10 @@
         <v>35</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>36</v>
@@ -7177,10 +7181,10 @@
         <v>36</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>36</v>
@@ -7191,10 +7195,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7205,7 +7209,7 @@
         <v>34</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>36</v>
@@ -7217,13 +7221,13 @@
         <v>36</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7274,13 +7278,13 @@
         <v>36</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>36</v>
@@ -7298,7 +7302,7 @@
         <v>36</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>36</v>
@@ -7309,14 +7313,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7335,16 +7339,16 @@
         <v>36</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7382,19 +7386,19 @@
         <v>36</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>34</v>
@@ -7403,10 +7407,10 @@
         <v>35</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>36</v>
@@ -7418,7 +7422,7 @@
         <v>36</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>36</v>
@@ -7429,10 +7433,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7440,10 +7444,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>36</v>
@@ -7452,29 +7456,29 @@
         <v>36</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>36</v>
@@ -7516,19 +7520,19 @@
         <v>36</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>36</v>
@@ -7537,10 +7541,10 @@
         <v>36</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>36</v>
@@ -7551,10 +7555,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7565,7 +7569,7 @@
         <v>34</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>36</v>
@@ -7574,19 +7578,19 @@
         <v>36</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7636,19 +7640,19 @@
         <v>36</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>36</v>
@@ -7657,10 +7661,10 @@
         <v>36</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>36</v>
@@ -7671,10 +7675,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7682,10 +7686,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>36</v>
@@ -7694,29 +7698,29 @@
         <v>36</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>36</v>
@@ -7758,19 +7762,19 @@
         <v>36</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>36</v>
@@ -7779,10 +7783,10 @@
         <v>36</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>36</v>
@@ -7793,10 +7797,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7807,7 +7811,7 @@
         <v>34</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>36</v>
@@ -7816,22 +7820,22 @@
         <v>36</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>36</v>
@@ -7880,19 +7884,19 @@
         <v>36</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>36</v>
@@ -7901,10 +7905,10 @@
         <v>36</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>36</v>
@@ -7915,10 +7919,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7929,7 +7933,7 @@
         <v>34</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>36</v>
@@ -7938,22 +7942,22 @@
         <v>36</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>36</v>
@@ -8002,19 +8006,19 @@
         <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>36</v>
@@ -8023,10 +8027,10 @@
         <v>36</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>36</v>
@@ -8037,10 +8041,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8051,7 +8055,7 @@
         <v>34</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>36</v>
@@ -8060,22 +8064,22 @@
         <v>36</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>36</v>
@@ -8124,19 +8128,19 @@
         <v>36</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>36</v>
@@ -8145,10 +8149,10 @@
         <v>36</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>36</v>
@@ -8159,10 +8163,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8170,34 +8174,34 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>36</v>
@@ -8246,34 +8250,34 @@
         <v>36</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>36</v>
@@ -8281,10 +8285,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8304,19 +8308,19 @@
         <v>36</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8366,7 +8370,7 @@
         <v>36</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>34</v>
@@ -8375,10 +8379,10 @@
         <v>35</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>36</v>
@@ -8387,13 +8391,13 @@
         <v>36</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>36</v>
@@ -8401,21 +8405,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>36</v>
@@ -8424,22 +8428,22 @@
         <v>36</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>36</v>
@@ -8488,34 +8492,34 @@
         <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>36</v>
@@ -8523,45 +8527,45 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>36</v>
@@ -8610,34 +8614,34 @@
         <v>36</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>36</v>
@@ -8645,10 +8649,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8659,7 +8663,7 @@
         <v>34</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>36</v>
@@ -8668,19 +8672,19 @@
         <v>36</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8730,19 +8734,19 @@
         <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>36</v>
@@ -8751,13 +8755,13 @@
         <v>36</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>36</v>
@@ -8765,10 +8769,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8788,22 +8792,22 @@
         <v>36</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>36</v>
@@ -8852,7 +8856,7 @@
         <v>36</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>34</v>
@@ -8861,25 +8865,25 @@
         <v>35</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>36</v>
@@ -8887,10 +8891,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8901,31 +8905,31 @@
         <v>34</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>36</v>
@@ -8962,94 +8966,94 @@
         <v>36</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>36</v>
@@ -9098,45 +9102,45 @@
         <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9147,7 +9151,7 @@
         <v>34</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>36</v>
@@ -9159,13 +9163,13 @@
         <v>36</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9216,13 +9220,13 @@
         <v>36</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>36</v>
@@ -9240,7 +9244,7 @@
         <v>36</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>36</v>
@@ -9251,14 +9255,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9277,16 +9281,16 @@
         <v>36</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9324,19 +9328,19 @@
         <v>36</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>34</v>
@@ -9345,10 +9349,10 @@
         <v>35</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>36</v>
@@ -9360,7 +9364,7 @@
         <v>36</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>36</v>
@@ -9371,10 +9375,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9382,34 +9386,34 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>36</v>
@@ -9458,19 +9462,19 @@
         <v>36</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>36</v>
@@ -9479,10 +9483,10 @@
         <v>36</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>36</v>
@@ -9493,10 +9497,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9507,37 +9511,37 @@
         <v>34</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>36</v>
@@ -9558,13 +9562,13 @@
         <v>36</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>36</v>
@@ -9582,19 +9586,19 @@
         <v>36</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>36</v>
@@ -9603,10 +9607,10 @@
         <v>36</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>36</v>
@@ -9617,10 +9621,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9628,34 +9632,34 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>36</v>
@@ -9704,19 +9708,19 @@
         <v>36</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>36</v>
@@ -9725,10 +9729,10 @@
         <v>36</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>36</v>
@@ -9739,10 +9743,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9750,41 +9754,41 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>36</v>
@@ -9826,19 +9830,19 @@
         <v>36</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>36</v>
@@ -9847,10 +9851,10 @@
         <v>36</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>36</v>
@@ -9861,10 +9865,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9872,41 +9876,41 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>36</v>
@@ -9948,19 +9952,19 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>36</v>
@@ -9969,10 +9973,10 @@
         <v>36</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>36</v>
@@ -9983,10 +9987,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9997,10 +10001,10 @@
         <v>34</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>36</v>
@@ -10009,19 +10013,19 @@
         <v>36</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>36</v>
@@ -10046,13 +10050,13 @@
         <v>36</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>36</v>
@@ -10070,19 +10074,19 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>36</v>
@@ -10091,10 +10095,10 @@
         <v>36</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>36</v>
@@ -10105,10 +10109,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10119,7 +10123,7 @@
         <v>34</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>36</v>
@@ -10131,13 +10135,13 @@
         <v>36</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10188,13 +10192,13 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>36</v>
@@ -10212,7 +10216,7 @@
         <v>36</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>36</v>
@@ -10223,14 +10227,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10249,16 +10253,16 @@
         <v>36</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10296,19 +10300,19 @@
         <v>36</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>34</v>
@@ -10317,10 +10321,10 @@
         <v>35</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>36</v>
@@ -10332,7 +10336,7 @@
         <v>36</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>36</v>
@@ -10343,10 +10347,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10366,22 +10370,22 @@
         <v>36</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>36</v>
@@ -10430,7 +10434,7 @@
         <v>36</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>34</v>
@@ -10439,10 +10443,10 @@
         <v>35</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>36</v>
@@ -10451,10 +10455,10 @@
         <v>36</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>36</v>
@@ -10465,10 +10469,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10479,7 +10483,7 @@
         <v>34</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>36</v>
@@ -10491,13 +10495,13 @@
         <v>36</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10548,13 +10552,13 @@
         <v>36</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>36</v>
@@ -10572,7 +10576,7 @@
         <v>36</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>36</v>
@@ -10583,14 +10587,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10609,16 +10613,16 @@
         <v>36</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10656,19 +10660,19 @@
         <v>36</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>34</v>
@@ -10677,10 +10681,10 @@
         <v>35</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>36</v>
@@ -10692,7 +10696,7 @@
         <v>36</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>36</v>
@@ -10703,10 +10707,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10714,10 +10718,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>36</v>
@@ -10726,22 +10730,22 @@
         <v>36</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>36</v>
@@ -10790,19 +10794,19 @@
         <v>36</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>36</v>
@@ -10811,10 +10815,10 @@
         <v>36</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>36</v>
@@ -10825,10 +10829,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10839,7 +10843,7 @@
         <v>34</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>36</v>
@@ -10848,19 +10852,19 @@
         <v>36</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10910,19 +10914,19 @@
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>36</v>
@@ -10931,10 +10935,10 @@
         <v>36</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>36</v>
@@ -10945,10 +10949,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10956,10 +10960,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>36</v>
@@ -10968,22 +10972,22 @@
         <v>36</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>36</v>
@@ -11032,19 +11036,19 @@
         <v>36</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>36</v>
@@ -11053,10 +11057,10 @@
         <v>36</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>36</v>
@@ -11067,10 +11071,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11081,7 +11085,7 @@
         <v>34</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>36</v>
@@ -11090,22 +11094,22 @@
         <v>36</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>36</v>
@@ -11154,19 +11158,19 @@
         <v>36</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>36</v>
@@ -11175,10 +11179,10 @@
         <v>36</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>36</v>
@@ -11189,10 +11193,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11203,7 +11207,7 @@
         <v>34</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>36</v>
@@ -11212,22 +11216,22 @@
         <v>36</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>36</v>
@@ -11276,19 +11280,19 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>36</v>
@@ -11297,10 +11301,10 @@
         <v>36</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>36</v>
@@ -11311,10 +11315,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11325,7 +11329,7 @@
         <v>34</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>36</v>
@@ -11334,22 +11338,22 @@
         <v>36</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>36</v>
@@ -11398,19 +11402,19 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>36</v>
@@ -11419,10 +11423,10 @@
         <v>36</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>36</v>
@@ -11433,14 +11437,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11459,19 +11463,19 @@
         <v>36</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>36</v>
@@ -11496,11 +11500,9 @@
         <v>36</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
         <v>476</v>
       </c>
@@ -11520,7 +11522,7 @@
         <v>36</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>34</v>
@@ -11529,10 +11531,10 @@
         <v>35</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>36</v>
@@ -11651,10 +11653,10 @@
         <v>35</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>36</v>
@@ -11691,7 +11693,7 @@
         <v>34</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>36</v>
@@ -11703,7 +11705,7 @@
         <v>36</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>490</v>
@@ -11738,7 +11740,7 @@
         <v>36</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y78" t="s" s="2">
         <v>493</v>
@@ -11768,13 +11770,13 @@
         <v>34</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>36</v>
@@ -11811,7 +11813,7 @@
         <v>34</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>36</v>
@@ -11823,7 +11825,7 @@
         <v>36</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>500</v>
@@ -11860,7 +11862,7 @@
         <v>36</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y79" t="s" s="2">
         <v>504</v>
@@ -11890,13 +11892,13 @@
         <v>34</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>36</v>
@@ -11933,7 +11935,7 @@
         <v>34</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>36</v>
@@ -12010,13 +12012,13 @@
         <v>34</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>36</v>
@@ -12053,7 +12055,7 @@
         <v>34</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>36</v>
@@ -12130,13 +12132,13 @@
         <v>34</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>36</v>
@@ -12255,7 +12257,7 @@
         <v>35</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>532</v>
@@ -12295,7 +12297,7 @@
         <v>34</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>36</v>
@@ -12307,13 +12309,13 @@
         <v>36</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12364,13 +12366,13 @@
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>36</v>
@@ -12388,7 +12390,7 @@
         <v>36</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>36</v>
@@ -12406,7 +12408,7 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12425,16 +12427,16 @@
         <v>36</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12472,19 +12474,19 @@
         <v>36</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>34</v>
@@ -12493,10 +12495,10 @@
         <v>35</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>36</v>
@@ -12508,7 +12510,7 @@
         <v>36</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>36</v>
@@ -12539,13 +12541,13 @@
         <v>36</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>539</v>
@@ -12554,10 +12556,10 @@
         <v>540</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>36</v>
@@ -12615,10 +12617,10 @@
         <v>35</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>36</v>
@@ -12630,7 +12632,7 @@
         <v>36</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>36</v>
@@ -12655,7 +12657,7 @@
         <v>34</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>36</v>
@@ -12732,7 +12734,7 @@
         <v>34</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>547</v>
@@ -12775,7 +12777,7 @@
         <v>34</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>36</v>
@@ -12852,7 +12854,7 @@
         <v>34</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>547</v>
@@ -12895,7 +12897,7 @@
         <v>34</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>36</v>
@@ -12907,7 +12909,7 @@
         <v>36</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>556</v>
@@ -12944,7 +12946,7 @@
         <v>36</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y88" t="s" s="2">
         <v>560</v>
@@ -12974,13 +12976,13 @@
         <v>34</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>36</v>
@@ -13029,7 +13031,7 @@
         <v>36</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>565</v>
@@ -13066,7 +13068,7 @@
         <v>36</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y89" t="s" s="2">
         <v>569</v>
@@ -13099,10 +13101,10 @@
         <v>35</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>36</v>
@@ -13139,7 +13141,7 @@
         <v>34</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>36</v>
@@ -13151,13 +13153,13 @@
         <v>36</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13208,13 +13210,13 @@
         <v>36</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>36</v>
@@ -13232,7 +13234,7 @@
         <v>36</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>36</v>
@@ -13250,7 +13252,7 @@
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13269,16 +13271,16 @@
         <v>36</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13316,19 +13318,19 @@
         <v>36</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>34</v>
@@ -13337,10 +13339,10 @@
         <v>35</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>36</v>
@@ -13352,7 +13354,7 @@
         <v>36</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>36</v>
@@ -13386,22 +13388,22 @@
         <v>36</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>36</v>
@@ -13450,7 +13452,7 @@
         <v>36</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>34</v>
@@ -13459,10 +13461,10 @@
         <v>35</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>36</v>
@@ -13471,10 +13473,10 @@
         <v>36</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>36</v>
@@ -13499,7 +13501,7 @@
         <v>34</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>36</v>
@@ -13511,13 +13513,13 @@
         <v>36</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13568,13 +13570,13 @@
         <v>36</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>36</v>
@@ -13592,7 +13594,7 @@
         <v>36</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>36</v>
@@ -13610,7 +13612,7 @@
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13629,16 +13631,16 @@
         <v>36</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13676,19 +13678,19 @@
         <v>36</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>34</v>
@@ -13697,10 +13699,10 @@
         <v>35</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>36</v>
@@ -13712,7 +13714,7 @@
         <v>36</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>36</v>
@@ -13734,10 +13736,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>36</v>
@@ -13746,22 +13748,22 @@
         <v>36</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>36</v>
@@ -13810,19 +13812,19 @@
         <v>36</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>36</v>
@@ -13831,10 +13833,10 @@
         <v>36</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>36</v>
@@ -13859,7 +13861,7 @@
         <v>34</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>36</v>
@@ -13868,19 +13870,19 @@
         <v>36</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13930,19 +13932,19 @@
         <v>36</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>36</v>
@@ -13951,10 +13953,10 @@
         <v>36</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>36</v>
@@ -13976,10 +13978,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>36</v>
@@ -13988,22 +13990,22 @@
         <v>36</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>36</v>
@@ -14052,19 +14054,19 @@
         <v>36</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>36</v>
@@ -14073,10 +14075,10 @@
         <v>36</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>36</v>
@@ -14101,7 +14103,7 @@
         <v>34</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>36</v>
@@ -14110,22 +14112,22 @@
         <v>36</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>36</v>
@@ -14174,19 +14176,19 @@
         <v>36</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>36</v>
@@ -14195,10 +14197,10 @@
         <v>36</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>36</v>
@@ -14223,7 +14225,7 @@
         <v>34</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>36</v>
@@ -14232,22 +14234,22 @@
         <v>36</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>36</v>
@@ -14296,19 +14298,19 @@
         <v>36</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>36</v>
@@ -14317,10 +14319,10 @@
         <v>36</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>36</v>
@@ -14345,7 +14347,7 @@
         <v>34</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>36</v>
@@ -14354,22 +14356,22 @@
         <v>36</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>36</v>
@@ -14418,19 +14420,19 @@
         <v>36</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>36</v>
@@ -14439,10 +14441,10 @@
         <v>36</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>36</v>
@@ -14467,7 +14469,7 @@
         <v>34</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>36</v>
@@ -14546,10 +14548,10 @@
         <v>34</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>588</v>
@@ -14589,7 +14591,7 @@
         <v>34</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>36</v>
@@ -14601,7 +14603,7 @@
         <v>36</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>592</v>
@@ -14610,7 +14612,7 @@
         <v>593</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14666,13 +14668,13 @@
         <v>34</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>36</v>
@@ -14718,7 +14720,7 @@
         <v>36</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K103" t="s" s="2">
         <v>596</v>
@@ -14789,10 +14791,10 @@
         <v>35</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>36</v>
@@ -14838,7 +14840,7 @@
         <v>36</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>603</v>
@@ -14909,10 +14911,10 @@
         <v>35</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>36</v>
@@ -14952,13 +14954,13 @@
         <v>35</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>527</v>
@@ -15031,7 +15033,7 @@
         <v>35</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>612</v>
@@ -15071,7 +15073,7 @@
         <v>34</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>36</v>
@@ -15083,13 +15085,13 @@
         <v>36</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15140,13 +15142,13 @@
         <v>36</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>36</v>
@@ -15164,7 +15166,7 @@
         <v>36</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>36</v>
@@ -15182,7 +15184,7 @@
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15201,16 +15203,16 @@
         <v>36</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15248,19 +15250,19 @@
         <v>36</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>34</v>
@@ -15269,10 +15271,10 @@
         <v>35</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>36</v>
@@ -15284,7 +15286,7 @@
         <v>36</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>36</v>
@@ -15315,13 +15317,13 @@
         <v>36</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>539</v>
@@ -15330,10 +15332,10 @@
         <v>540</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>36</v>
@@ -15391,10 +15393,10 @@
         <v>35</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>36</v>
@@ -15406,7 +15408,7 @@
         <v>36</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>36</v>
@@ -15428,22 +15430,22 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>619</v>
@@ -15480,13 +15482,13 @@
         <v>36</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>36</v>
@@ -15507,16 +15509,16 @@
         <v>618</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>36</v>
@@ -15525,13 +15527,13 @@
         <v>623</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>36</v>
@@ -15553,19 +15555,19 @@
         <v>34</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>625</v>
@@ -15577,7 +15579,7 @@
         <v>627</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>36</v>
@@ -15602,7 +15604,7 @@
         <v>36</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y110" t="s" s="2">
         <v>628</v>
@@ -15632,13 +15634,13 @@
         <v>34</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>630</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>36</v>
@@ -15647,16 +15649,16 @@
         <v>631</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="111" hidden="true">
@@ -15675,10 +15677,10 @@
         <v>34</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>36</v>
@@ -15687,7 +15689,7 @@
         <v>36</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>633</v>
@@ -15699,7 +15701,7 @@
         <v>635</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>36</v>
@@ -15724,13 +15726,13 @@
         <v>36</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>36</v>
@@ -15754,13 +15756,13 @@
         <v>34</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>636</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>36</v>
@@ -15769,10 +15771,10 @@
         <v>36</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>36</v>
@@ -15790,7 +15792,7 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15809,19 +15811,19 @@
         <v>36</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>36</v>
@@ -15846,10 +15848,10 @@
         <v>36</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>475</v>
+        <v>638</v>
       </c>
       <c r="Z112" t="s" s="2">
         <v>476</v>
@@ -15879,10 +15881,10 @@
         <v>35</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>36</v>
@@ -15905,10 +15907,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15934,10 +15936,10 @@
         <v>37</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>530</v>
@@ -15992,7 +15994,7 @@
         <v>36</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>34</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-23T10:14:09+00:00</t>
+    <t>2023-11-28T12:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,11 +440,10 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.</t>
-  </si>
-  <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -12326,7 +12326,7 @@
         <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bmi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
